--- a/backend/assets/templates/registo-riscos.xlsx
+++ b/backend/assets/templates/registo-riscos.xlsx
@@ -49,22 +49,22 @@
     <t xml:space="preserve">📈  PAINEL DE CONTROLO — Dashboard de resumo para apresentação à gestão de topo</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠️  COMO USAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Preencha as células AMARELAS no Registo de Riscos com os dados da sua empresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Use os menus dropdown para Probabilidade, Impacto, Estado e Responsável. A coluna Origem indica a fonte de cada risco: Scan (detetado pelo scanner CISPLAN), Questionário (derivado da autoavaliação) ou Manual (adicionado pela empresa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. O Nível de Risco é calculado automaticamente (Probabilidade × Impacto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Reveja e atualize pelo menos 1×/ano ou após incidente significativo (obrigação NIS2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Apresente o resumo do Painel de Controlo na reunião anual de cibersegurança com a gestão</t>
+    <t xml:space="preserve">⚠️  COMO USAR ESTE DOCUMENTO PRÉ-PREENCHIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Os riscos com Origem = "Scan" foram identificados e pré-avaliados automaticamente a partir do scan CISPLAN — reveja-os e ajuste Probabilidade e Impacto à realidade da sua empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Acrescente riscos que o scan não deteta (ex.: falhas de processo, fornecedores, pessoas) em linhas novas, marcando a coluna Origem como "Manual"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Preencha o Responsável de cada risco e atualize o Estado à medida que as medidas de tratamento são aplicadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. O Nível de Risco é calculado automaticamente (Probabilidade × Impacto) — não precisa de o preencher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Reveja pelo menos 1×/ano ou após incidente significativo (obrigação NIS2) e apresente o Painel de Controlo à gestão de topo</t>
   </si>
   <si>
     <t xml:space="preserve">📏  ESCALA DE AVALIAÇÃO</t>
@@ -311,25 +311,25 @@
     <t xml:space="preserve">LEGENDA</t>
   </si>
   <si>
-    <t xml:space="preserve">🟢 BAIXO (1-4)</t>
+    <t xml:space="preserve">BAIXO (1-4)</t>
   </si>
   <si>
     <t xml:space="preserve">Monitorizar. Sem ação urgente necessária.</t>
   </si>
   <si>
-    <t xml:space="preserve">🟡 MÉDIO (5-9)</t>
+    <t xml:space="preserve">MÉDIO (5-9)</t>
   </si>
   <si>
     <t xml:space="preserve">Planear medidas de mitigação no próximo ciclo.</t>
   </si>
   <si>
-    <t xml:space="preserve">🟠 ALTO (10-16)</t>
+    <t xml:space="preserve">ALTO (10-16)</t>
   </si>
   <si>
     <t xml:space="preserve">Ação prioritária. Tratar no prazo de 90 dias.</t>
   </si>
   <si>
-    <t xml:space="preserve">🔴 CRÍTICO (17-25)</t>
+    <t xml:space="preserve">CRÍTICO (17-25)</t>
   </si>
   <si>
     <t xml:space="preserve">Ação imediata. Escalar para gestão de topo.</t>
@@ -609,7 +609,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -668,6 +668,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
         <bgColor rgb="FFFDECEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BE7B"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB84"/>
+        <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8A15A"/>
+        <bgColor rgb="FFFF99CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8696B"/>
+        <bgColor rgb="FFC55A11"/>
       </patternFill>
     </fill>
   </fills>
@@ -804,7 +828,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -953,6 +977,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="19" fillId="9" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -961,6 +989,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="20" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -969,12 +1001,20 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1139,9 +1179,9 @@
       <rgbColor rgb="FFFFF3CD"/>
       <rgbColor rgb="FFE2F0EA"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFF8696B"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFFDECEA"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1153,16 +1193,16 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFEBF3FB"/>
       <rgbColor rgb="FFF4F4F4"/>
-      <rgbColor rgb="FFFDECEA"/>
+      <rgbColor rgb="FFFFEB84"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF2E75B6"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF63BE7B"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFF8A15A"/>
       <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
@@ -1633,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="18" t="str">
-        <f aca="false">IF(H8&gt;=17,"🔴 CRÍTICO",IF(H8&gt;=10,"🟠 ALTO",IF(H8&gt;=5,"🟡 MÉDIO",IF(H8&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H8&gt;=17,"CRÍTICO",IF(H8&gt;=10,"ALTO",IF(H8&gt;=5,"MÉDIO",IF(H8&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J8" s="14"/>
@@ -1655,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="21" t="str">
-        <f aca="false">IF(H9&gt;=17,"🔴 CRÍTICO",IF(H9&gt;=10,"🟠 ALTO",IF(H9&gt;=5,"🟡 MÉDIO",IF(H9&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H9&gt;=17,"CRÍTICO",IF(H9&gt;=10,"ALTO",IF(H9&gt;=5,"MÉDIO",IF(H9&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J9" s="19"/>
@@ -1677,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="18" t="str">
-        <f aca="false">IF(H10&gt;=17,"🔴 CRÍTICO",IF(H10&gt;=10,"🟠 ALTO",IF(H10&gt;=5,"🟡 MÉDIO",IF(H10&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H10&gt;=17,"CRÍTICO",IF(H10&gt;=10,"ALTO",IF(H10&gt;=5,"MÉDIO",IF(H10&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J10" s="14"/>
@@ -1699,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="21" t="str">
-        <f aca="false">IF(H11&gt;=17,"🔴 CRÍTICO",IF(H11&gt;=10,"🟠 ALTO",IF(H11&gt;=5,"🟡 MÉDIO",IF(H11&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H11&gt;=17,"CRÍTICO",IF(H11&gt;=10,"ALTO",IF(H11&gt;=5,"MÉDIO",IF(H11&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J11" s="19"/>
@@ -1721,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="18" t="str">
-        <f aca="false">IF(H12&gt;=17,"🔴 CRÍTICO",IF(H12&gt;=10,"🟠 ALTO",IF(H12&gt;=5,"🟡 MÉDIO",IF(H12&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H12&gt;=17,"CRÍTICO",IF(H12&gt;=10,"ALTO",IF(H12&gt;=5,"MÉDIO",IF(H12&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J12" s="14"/>
@@ -1743,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="21" t="str">
-        <f aca="false">IF(H13&gt;=17,"🔴 CRÍTICO",IF(H13&gt;=10,"🟠 ALTO",IF(H13&gt;=5,"🟡 MÉDIO",IF(H13&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H13&gt;=17,"CRÍTICO",IF(H13&gt;=10,"ALTO",IF(H13&gt;=5,"MÉDIO",IF(H13&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J13" s="19"/>
@@ -1765,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="18" t="str">
-        <f aca="false">IF(H14&gt;=17,"🔴 CRÍTICO",IF(H14&gt;=10,"🟠 ALTO",IF(H14&gt;=5,"🟡 MÉDIO",IF(H14&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H14&gt;=17,"CRÍTICO",IF(H14&gt;=10,"ALTO",IF(H14&gt;=5,"MÉDIO",IF(H14&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J14" s="14"/>
@@ -1787,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="21" t="str">
-        <f aca="false">IF(H15&gt;=17,"🔴 CRÍTICO",IF(H15&gt;=10,"🟠 ALTO",IF(H15&gt;=5,"🟡 MÉDIO",IF(H15&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H15&gt;=17,"CRÍTICO",IF(H15&gt;=10,"ALTO",IF(H15&gt;=5,"MÉDIO",IF(H15&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J15" s="19"/>
@@ -1809,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="18" t="str">
-        <f aca="false">IF(H16&gt;=17,"🔴 CRÍTICO",IF(H16&gt;=10,"🟠 ALTO",IF(H16&gt;=5,"🟡 MÉDIO",IF(H16&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H16&gt;=17,"CRÍTICO",IF(H16&gt;=10,"ALTO",IF(H16&gt;=5,"MÉDIO",IF(H16&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J16" s="14"/>
@@ -1831,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="21" t="str">
-        <f aca="false">IF(H17&gt;=17,"🔴 CRÍTICO",IF(H17&gt;=10,"🟠 ALTO",IF(H17&gt;=5,"🟡 MÉDIO",IF(H17&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H17&gt;=17,"CRÍTICO",IF(H17&gt;=10,"ALTO",IF(H17&gt;=5,"MÉDIO",IF(H17&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J17" s="19"/>
@@ -1853,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="26" t="str">
-        <f aca="false">IF(H18&gt;=17,"🔴 CRÍTICO",IF(H18&gt;=10,"🟠 ALTO",IF(H18&gt;=5,"🟡 MÉDIO",IF(H18&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H18&gt;=17,"CRÍTICO",IF(H18&gt;=10,"ALTO",IF(H18&gt;=5,"MÉDIO",IF(H18&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J18" s="22"/>
@@ -1875,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="29" t="str">
-        <f aca="false">IF(H19&gt;=17,"🔴 CRÍTICO",IF(H19&gt;=10,"🟠 ALTO",IF(H19&gt;=5,"🟡 MÉDIO",IF(H19&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H19&gt;=17,"CRÍTICO",IF(H19&gt;=10,"ALTO",IF(H19&gt;=5,"MÉDIO",IF(H19&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J19" s="27"/>
@@ -1897,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="26" t="str">
-        <f aca="false">IF(H20&gt;=17,"🔴 CRÍTICO",IF(H20&gt;=10,"🟠 ALTO",IF(H20&gt;=5,"🟡 MÉDIO",IF(H20&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H20&gt;=17,"CRÍTICO",IF(H20&gt;=10,"ALTO",IF(H20&gt;=5,"MÉDIO",IF(H20&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J20" s="22"/>
@@ -1919,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="29" t="str">
-        <f aca="false">IF(H21&gt;=17,"🔴 CRÍTICO",IF(H21&gt;=10,"🟠 ALTO",IF(H21&gt;=5,"🟡 MÉDIO",IF(H21&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H21&gt;=17,"CRÍTICO",IF(H21&gt;=10,"ALTO",IF(H21&gt;=5,"MÉDIO",IF(H21&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J21" s="27"/>
@@ -1941,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="26" t="str">
-        <f aca="false">IF(H22&gt;=17,"🔴 CRÍTICO",IF(H22&gt;=10,"🟠 ALTO",IF(H22&gt;=5,"🟡 MÉDIO",IF(H22&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H22&gt;=17,"CRÍTICO",IF(H22&gt;=10,"ALTO",IF(H22&gt;=5,"MÉDIO",IF(H22&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J22" s="22"/>
@@ -1963,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="29" t="str">
-        <f aca="false">IF(H23&gt;=17,"🔴 CRÍTICO",IF(H23&gt;=10,"🟠 ALTO",IF(H23&gt;=5,"🟡 MÉDIO",IF(H23&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H23&gt;=17,"CRÍTICO",IF(H23&gt;=10,"ALTO",IF(H23&gt;=5,"MÉDIO",IF(H23&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J23" s="27"/>
@@ -1985,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="26" t="str">
-        <f aca="false">IF(H24&gt;=17,"🔴 CRÍTICO",IF(H24&gt;=10,"🟠 ALTO",IF(H24&gt;=5,"🟡 MÉDIO",IF(H24&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H24&gt;=17,"CRÍTICO",IF(H24&gt;=10,"ALTO",IF(H24&gt;=5,"MÉDIO",IF(H24&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J24" s="22"/>
@@ -2007,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="29" t="str">
-        <f aca="false">IF(H25&gt;=17,"🔴 CRÍTICO",IF(H25&gt;=10,"🟠 ALTO",IF(H25&gt;=5,"🟡 MÉDIO",IF(H25&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H25&gt;=17,"CRÍTICO",IF(H25&gt;=10,"ALTO",IF(H25&gt;=5,"MÉDIO",IF(H25&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J25" s="27"/>
@@ -2029,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="26" t="str">
-        <f aca="false">IF(H26&gt;=17,"🔴 CRÍTICO",IF(H26&gt;=10,"🟠 ALTO",IF(H26&gt;=5,"🟡 MÉDIO",IF(H26&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H26&gt;=17,"CRÍTICO",IF(H26&gt;=10,"ALTO",IF(H26&gt;=5,"MÉDIO",IF(H26&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J26" s="22"/>
@@ -2051,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="29" t="str">
-        <f aca="false">IF(H27&gt;=17,"🔴 CRÍTICO",IF(H27&gt;=10,"🟠 ALTO",IF(H27&gt;=5,"🟡 MÉDIO",IF(H27&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H27&gt;=17,"CRÍTICO",IF(H27&gt;=10,"ALTO",IF(H27&gt;=5,"MÉDIO",IF(H27&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J27" s="27"/>
@@ -2073,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="29" t="str">
-        <f aca="false">IF(H28&gt;=17,"🔴 CRÍTICO",IF(H28&gt;=10,"🟠 ALTO",IF(H28&gt;=5,"🟡 MÉDIO",IF(H28&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H28&gt;=17,"CRÍTICO",IF(H28&gt;=10,"ALTO",IF(H28&gt;=5,"MÉDIO",IF(H28&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J28" s="27"/>
@@ -2095,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="29" t="str">
-        <f aca="false">IF(H29&gt;=17,"🔴 CRÍTICO",IF(H29&gt;=10,"🟠 ALTO",IF(H29&gt;=5,"🟡 MÉDIO",IF(H29&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H29&gt;=17,"CRÍTICO",IF(H29&gt;=10,"ALTO",IF(H29&gt;=5,"MÉDIO",IF(H29&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J29" s="27"/>
@@ -2117,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="29" t="str">
-        <f aca="false">IF(H30&gt;=17,"🔴 CRÍTICO",IF(H30&gt;=10,"🟠 ALTO",IF(H30&gt;=5,"🟡 MÉDIO",IF(H30&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H30&gt;=17,"CRÍTICO",IF(H30&gt;=10,"ALTO",IF(H30&gt;=5,"MÉDIO",IF(H30&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J30" s="27"/>
@@ -2139,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="29" t="str">
-        <f aca="false">IF(H31&gt;=17,"🔴 CRÍTICO",IF(H31&gt;=10,"🟠 ALTO",IF(H31&gt;=5,"🟡 MÉDIO",IF(H31&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H31&gt;=17,"CRÍTICO",IF(H31&gt;=10,"ALTO",IF(H31&gt;=5,"MÉDIO",IF(H31&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J31" s="27"/>
@@ -2161,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="29" t="str">
-        <f aca="false">IF(H32&gt;=17,"🔴 CRÍTICO",IF(H32&gt;=10,"🟠 ALTO",IF(H32&gt;=5,"🟡 MÉDIO",IF(H32&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H32&gt;=17,"CRÍTICO",IF(H32&gt;=10,"ALTO",IF(H32&gt;=5,"MÉDIO",IF(H32&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J32" s="27"/>
@@ -2183,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="29" t="str">
-        <f aca="false">IF(H33&gt;=17,"🔴 CRÍTICO",IF(H33&gt;=10,"🟠 ALTO",IF(H33&gt;=5,"🟡 MÉDIO",IF(H33&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H33&gt;=17,"CRÍTICO",IF(H33&gt;=10,"ALTO",IF(H33&gt;=5,"MÉDIO",IF(H33&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J33" s="27"/>
@@ -2205,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="29" t="str">
-        <f aca="false">IF(H34&gt;=17,"🔴 CRÍTICO",IF(H34&gt;=10,"🟠 ALTO",IF(H34&gt;=5,"🟡 MÉDIO",IF(H34&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H34&gt;=17,"CRÍTICO",IF(H34&gt;=10,"ALTO",IF(H34&gt;=5,"MÉDIO",IF(H34&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J34" s="27"/>
@@ -2227,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="29" t="str">
-        <f aca="false">IF(H35&gt;=17,"🔴 CRÍTICO",IF(H35&gt;=10,"🟠 ALTO",IF(H35&gt;=5,"🟡 MÉDIO",IF(H35&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H35&gt;=17,"CRÍTICO",IF(H35&gt;=10,"ALTO",IF(H35&gt;=5,"MÉDIO",IF(H35&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J35" s="27"/>
@@ -2249,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="29" t="str">
-        <f aca="false">IF(H36&gt;=17,"🔴 CRÍTICO",IF(H36&gt;=10,"🟠 ALTO",IF(H36&gt;=5,"🟡 MÉDIO",IF(H36&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H36&gt;=17,"CRÍTICO",IF(H36&gt;=10,"ALTO",IF(H36&gt;=5,"MÉDIO",IF(H36&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J36" s="27"/>
@@ -2271,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="29" t="str">
-        <f aca="false">IF(H37&gt;=17,"🔴 CRÍTICO",IF(H37&gt;=10,"🟠 ALTO",IF(H37&gt;=5,"🟡 MÉDIO",IF(H37&gt;0,"🟢 BAIXO",""))))</f>
+        <f aca="false">IF(H37&gt;=17,"CRÍTICO",IF(H37&gt;=10,"ALTO",IF(H37&gt;=5,"MÉDIO",IF(H37&gt;0,"BAIXO",""))))</f>
         <v/>
       </c>
       <c r="J37" s="27"/>
@@ -2332,7 +2372,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G17"/>
+  <dimension ref="A2:G17"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -2498,52 +2538,56 @@
       <c r="G13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="37" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38" t="s">
+      <c r="C14" s="38"/>
+      <c r="D14" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="39" t="s">
+      <c r="A15" s="40"/>
+      <c r="B15" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="41" t="s">
+      <c r="A16" s="43"/>
+      <c r="B16" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42" t="s">
+      <c r="C16" s="44"/>
+      <c r="D16" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="43" t="s">
+      <c r="A17" s="46"/>
+      <c r="B17" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="44" t="s">
+      <c r="C17" s="47"/>
+      <c r="D17" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2588,136 +2632,136 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="52" t="n">
         <f aca="false">COUNTA('🎯 REGISTO DE RISCOS'!C8:C40)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="54" t="n">
         <f aca="false">COUNTIF('🎯 REGISTO DE RISCOS'!H8:H40,"&gt;="&amp;17)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="52" t="n">
+      <c r="C7" s="56" t="n">
         <f aca="false">COUNTIFS('🎯 REGISTO DE RISCOS'!H8:H40,"&gt;="&amp;10,'🎯 REGISTO DE RISCOS'!H8:H40,"&lt;"&amp;17)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="58" t="n">
         <f aca="false">COUNTIFS('🎯 REGISTO DE RISCOS'!H8:H40,"&gt;="&amp;5,'🎯 REGISTO DE RISCOS'!H8:H40,"&lt;"&amp;10)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="56" t="n">
+      <c r="C9" s="60" t="n">
         <f aca="false">COUNTIFS('🎯 REGISTO DE RISCOS'!H8:H40,"&gt;="&amp;1,'🎯 REGISTO DE RISCOS'!H8:H40,"&lt;"&amp;5)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="54" t="n">
+      <c r="C12" s="58" t="n">
         <f aca="false">COUNTIF('🎯 REGISTO DE RISCOS'!L8:L40,"Em curso")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="56" t="n">
+      <c r="C13" s="60" t="n">
         <f aca="false">COUNTIF('🎯 REGISTO DE RISCOS'!L8:L40,"Concluído")</f>
         <v>0</v>
       </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="61" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="58" t="n">
+      <c r="C14" s="62" t="n">
         <f aca="false">COUNTIF('🎯 REGISTO DE RISCOS'!L8:L40,"Transferir (Seguro)")</f>
         <v>0</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/backend/assets/templates/registo-riscos.xlsx
+++ b/backend/assets/templates/registo-riscos.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">2. Acrescente riscos que o scan não deteta (ex.: falhas de processo, fornecedores, pessoas) em linhas novas, marcando a coluna Origem como "Manual"</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Preencha o Responsável de cada risco e atualize o Estado à medida que as medidas de tratamento são aplicadas</t>
+    <t xml:space="preserve">3. Preencha, para cada risco: o RESPONSÁVEL (quem trata) e o ESTADO na coluna "Estado" (Em curso / Concluído / Transferido). O Painel de Controlo atualiza-se automaticamente a partir desta coluna — enquanto não a preencher, o Painel mostra 0 riscos tratados (é normal).</t>
   </si>
   <si>
     <t xml:space="preserve">4. O Nível de Risco é calculado automaticamente (Probabilidade × Impacto) — não precisa de o preencher</t>
@@ -977,7 +977,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -989,7 +989,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1001,7 +1001,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1013,7 +1013,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
